--- a/public/downloads/send-back-cost-check.xlsx
+++ b/public/downloads/send-back-cost-check.xlsx
@@ -1624,6 +1624,11 @@
           <t>The five checks</t>
         </is>
       </c>
+      <c r="C39" s="13" t="inlineStr">
+        <is>
+          <t>Pass — nothing to do here.   ·   Attention — it works today, and something about it will surprise you.   ·   Fail — this is the one that stops you scaling, fix it first.</t>
+        </is>
+      </c>
     </row>
     <row r="40" ht="20" customHeight="1">
       <c r="A40" s="30" t="inlineStr">
@@ -1654,7 +1659,7 @@
       <c r="J40" s="30" t="n"/>
       <c r="K40" s="30" t="n"/>
     </row>
-    <row r="41" ht="30" customHeight="1">
+    <row r="41" ht="46" customHeight="1">
       <c r="A41" s="31" t="n">
         <v>1</v>
       </c>
@@ -1667,12 +1672,12 @@
         <f>IF(COUNTIF(B14:B20,"Yes")=0,"Not answered",IF(COUNTIFS(B14:B20,"Yes",D14:D20,"")&gt;0,"Fail","Pass"))</f>
         <v/>
       </c>
-      <c r="G41" s="13">
-        <f>IF(COUNTIF(B14:B20,"Yes")=0,"No path is marked as present yet.",IF(COUNTIFS(B14:B20,"Yes",D14:D20,"")&gt;0,"A present path has no average rounds. A path you cannot count is a path you cannot cost.","Every present path says how often it sends work back."))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="42" ht="30" customHeight="1">
+      <c r="G41" s="14">
+        <f>(IF(COUNTIF(B14:B20,"Yes")=0,"No path is marked as present yet.",IF(COUNTIFS(B14:B20,"Yes",D14:D20,"")&gt;0,"A present path has no average rounds. A path you cannot count is a path you cannot cost.","Every present path says how often it sends work back.")))&amp;IF((IF(COUNTIF(B14:B20,"Yes")=0,"",IF(COUNTIFS(B14:B20,"Yes",D14:D20,"")&gt;0,"Count send-backs divided by tasks over a normal week, from your judge verdicts, validation errors, tool errors and review queue.","")))="","",CHAR(10)&amp;"Do this: "&amp;(IF(COUNTIF(B14:B20,"Yes")=0,"",IF(COUNTIFS(B14:B20,"Yes",D14:D20,"")&gt;0,"Count send-backs divided by tasks over a normal week, from your judge verdicts, validation errors, tool errors and review queue.",""))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42" ht="46" customHeight="1">
       <c r="A42" s="31" t="n">
         <v>2</v>
       </c>
@@ -1685,12 +1690,12 @@
         <f>IF(COUNTIF(B14:B20,"Yes")=0,"Not answered",IF(COUNTIFS(B14:B20,"Yes",E14:E20,"")+COUNTIFS(B14:B20,"Yes",F14:F20,"")+COUNTIFS(B14:B20,"Yes",G14:G20,"")&gt;0,"Fail",IF(COUNTIFS(B15:B18,"Yes",G15:G18,0)&gt;0,"Attention","Pass")))</f>
         <v/>
       </c>
-      <c r="G42" s="13">
-        <f>IF(COUNTIF(B14:B20,"Yes")=0,"No path is marked as present yet.",IF(COUNTIFS(B14:B20,"Yes",E14:E20,"")+COUNTIFS(B14:B20,"Yes",F14:F20,"")+COUNTIFS(B14:B20,"Yes",G14:G20,"")&gt;0,"A present path is missing repeated, review or growth. Zero is a valid answer; blank is not.",IF(COUNTIFS(B15:B18,"Yes",G15:G18,0)&gt;0,"A judge, validation, tool or human path has no context growth. Redos usually carry more context. Check this.","Every present path has all three parts of a round.")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="43" ht="30" customHeight="1">
+      <c r="G42" s="14">
+        <f>(IF(COUNTIF(B14:B20,"Yes")=0,"No path is marked as present yet.",IF(COUNTIFS(B14:B20,"Yes",E14:E20,"")+COUNTIFS(B14:B20,"Yes",F14:F20,"")+COUNTIFS(B14:B20,"Yes",G14:G20,"")&gt;0,"A present path is missing repeated, review or growth. Zero is a valid answer; blank is not.",IF(COUNTIFS(B15:B18,"Yes",G15:G18,0)&gt;0,"A judge, validation, tool or human path has no context growth. Redos usually carry more context. Check this.","Every present path has all three parts of a round."))))&amp;IF((IF(COUNTIF(B14:B20,"Yes")=0,"",IF(COUNTIFS(B14:B20,"Yes",E14:E20,"")+COUNTIFS(B14:B20,"Yes",F14:F20,"")+COUNTIFS(B14:B20,"Yes",G14:G20,"")&gt;0,"Open one trace that was sent back and read the three figures off it: the tokens of the steps that ran again, the checker's own call, and how much bigger the redo's input was.",IF(COUNTIFS(B15:B18,"Yes",G15:G18,0)&gt;0,"Compare the input tokens of the first attempt with the redo in one trace. If the critique, the error or the rejected draft is carried forward, growth is not zero.",""))))="","",CHAR(10)&amp;"Do this: "&amp;(IF(COUNTIF(B14:B20,"Yes")=0,"",IF(COUNTIFS(B14:B20,"Yes",E14:E20,"")+COUNTIFS(B14:B20,"Yes",F14:F20,"")+COUNTIFS(B14:B20,"Yes",G14:G20,"")&gt;0,"Open one trace that was sent back and read the three figures off it: the tokens of the steps that ran again, the checker's own call, and how much bigger the redo's input was.",IF(COUNTIFS(B15:B18,"Yes",G15:G18,0)&gt;0,"Compare the input tokens of the first attempt with the redo in one trace. If the critique, the error or the rejected draft is carried forward, growth is not zero.","")))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43" ht="46" customHeight="1">
       <c r="A43" s="31" t="n">
         <v>3</v>
       </c>
@@ -1703,12 +1708,12 @@
         <f>IF(COUNTIF(B14:B20,"Yes")=0,"Not answered",IF(OR(SUM(R14:R20)&gt;0,COUNTIFS(B14:B20,"Yes",J14:J20,"")+COUNTIFS(B14:B20,"Yes",J14:J20,"Not decided")&gt;0),"Fail",IF(COUNTIFS(B14:B20,"Yes",K14:K20,"")&gt;0,"Attention","Pass")))</f>
         <v/>
       </c>
-      <c r="G43" s="13">
-        <f>IF(COUNTIF(B14:B20,"Yes")=0,"No path is marked as present yet.",IF(SUM(R14:R20)&gt;0,"A present path has no cap. Without one the worst case has no ceiling.",IF(COUNTIFS(B14:B20,"Yes",J14:J20,"")+COUNTIFS(B14:B20,"Yes",J14:J20,"Not decided")&gt;0,"A present path has no decided outcome after the last round.",IF(COUNTIFS(B14:B20,"Yes",K14:K20,"")&gt;0,"A path is capped with an outcome, but nobody owns it.","Every present path is capped, with a decided outcome and a named owner."))))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="44" ht="30" customHeight="1">
+      <c r="G43" s="14">
+        <f>(IF(COUNTIF(B14:B20,"Yes")=0,"No path is marked as present yet.",IF(SUM(R14:R20)&gt;0,"A present path has no cap. Without one the worst case has no ceiling.",IF(COUNTIFS(B14:B20,"Yes",J14:J20,"")+COUNTIFS(B14:B20,"Yes",J14:J20,"Not decided")&gt;0,"A present path has no decided outcome after the last round.",IF(COUNTIFS(B14:B20,"Yes",K14:K20,"")&gt;0,"A path is capped with an outcome, but nobody owns it.","Every present path is capped, with a decided outcome and a named owner.")))))&amp;IF((IF(COUNTIF(B14:B20,"Yes")=0,"",IF(SUM(R14:R20)&gt;0,"Set a maximum rounds per task in your orchestrator, and decide what the agent does after the last one: fail and tell the user, hand to a human, ship with a warning, or queue it.",IF(COUNTIFS(B14:B20,"Yes",J14:J20,"")+COUNTIFS(B14:B20,"Yes",J14:J20,"Not decided")&gt;0,"Decide what the agent does after the last round: fail and tell the user, hand to a human, ship with a warning, or queue it.",IF(COUNTIFS(B14:B20,"Yes",K14:K20,"")&gt;0,"Name the person or team who picks it up when that outcome fires.","")))))="","",CHAR(10)&amp;"Do this: "&amp;(IF(COUNTIF(B14:B20,"Yes")=0,"",IF(SUM(R14:R20)&gt;0,"Set a maximum rounds per task in your orchestrator, and decide what the agent does after the last one: fail and tell the user, hand to a human, ship with a warning, or queue it.",IF(COUNTIFS(B14:B20,"Yes",J14:J20,"")+COUNTIFS(B14:B20,"Yes",J14:J20,"Not decided")&gt;0,"Decide what the agent does after the last round: fail and tell the user, hand to a human, ship with a warning, or queue it.",IF(COUNTIFS(B14:B20,"Yes",K14:K20,"")&gt;0,"Name the person or team who picks it up when that outcome fires.",""))))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44" ht="46" customHeight="1">
       <c r="A44" s="31" t="n">
         <v>4</v>
       </c>
@@ -1721,12 +1726,12 @@
         <f>IF((SUM(R14:R20)&gt;0),"Fail",IF(OR(C31="",C35=""),"Not answered",IF(C31&gt;1,"Fail",IF(AND(C31&lt;=0.8,C35&lt;=1),"Pass","Attention"))))</f>
         <v/>
       </c>
-      <c r="G44" s="13">
-        <f>IF((SUM(R14:R20)&gt;0),"The worst case is unbounded, so there is no availability number to check.",IF(OR(C31="",C35=""),"Peak tasks per minute and the quota are needed for this one.",IF(C31&gt;1,"Your normal load already exceeds the quota.",IF(AND(C31&lt;=0.8,C35&lt;=1),"Normal load has headroom, and the worst case still fits.",IF(C31&lt;=0.8,"Normal load has headroom, but the worst case goes over the quota.","Normal load is above 80% of the quota. Any spike tips it over.")))))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="45" ht="30" customHeight="1">
+      <c r="G44" s="14">
+        <f>(IF((SUM(R14:R20)&gt;0),"The worst case is unbounded, so there is no availability number to check.",IF(OR(C31="",C35=""),"Peak tasks per minute and the quota are needed for this one.",IF(C31&gt;1,"Your normal load already exceeds the quota.",IF(AND(C31&lt;=0.8,C35&lt;=1),"Normal load has headroom, and the worst case still fits.",IF(C31&lt;=0.8,"Normal load has headroom, but the worst case goes over the quota.","Normal load is above 80% of the quota. Any spike tips it over."))))))&amp;IF((IF((SUM(R14:R20)&gt;0),"Cap every present path first. Until then there is no worst case to compare against the quota.",IF(OR(C31="",C35=""),"",IF(C31&gt;1,"Cut what a round costs, lower the average rounds, or raise the quota. The path with the largest average rounds times round cost is the lever; on most workflows that is the judge.",IF(AND(C31&lt;=0.8,C35&lt;=1),"",IF(C31&lt;=0.8,"Lower the caps, or add a circuit breaker that stops new work once the refusal rate crosses a threshold, so a bad minute cannot reach the worst case.","Get normal load under 80% of the quota: cut the round cost, cut the average rounds, or raise the quota."))))))="","",CHAR(10)&amp;"Do this: "&amp;(IF((SUM(R14:R20)&gt;0),"Cap every present path first. Until then there is no worst case to compare against the quota.",IF(OR(C31="",C35=""),"",IF(C31&gt;1,"Cut what a round costs, lower the average rounds, or raise the quota. The path with the largest average rounds times round cost is the lever; on most workflows that is the judge.",IF(AND(C31&lt;=0.8,C35&lt;=1),"",IF(C31&lt;=0.8,"Lower the caps, or add a circuit breaker that stops new work once the refusal rate crosses a threshold, so a bad minute cannot reach the worst case.","Get normal load under 80% of the quota: cut the round cost, cut the average rounds, or raise the quota.")))))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45" ht="46" customHeight="1">
       <c r="A45" s="31" t="n">
         <v>5</v>
       </c>
@@ -1739,25 +1744,25 @@
         <f>IF(C24="","Not answered",IF(C24&lt;&gt;"Per task, across all rounds","Fail",IF(OR(C23="",C28=""),"Not answered",IF(C23&lt;C28,"Fail",IF(OR((SUM(R14:R20)&gt;0),AND(C32&lt;&gt;"",C32&lt;&gt;"Unbounded",C32&gt;C23)),"Pass",IF(C32="","Not answered","Attention"))))))</f>
         <v/>
       </c>
-      <c r="G45" s="13">
-        <f>IF(C24="","Say how the budget is enforced.",IF(C24="Per call only","A per-call budget never sees the rounds add up. The task is what costs money.",IF(C24="Not enforced","Nothing stops a task at a token total.",IF(OR(C23="",C28=""),"Enter a per-task budget to check it against the two totals.",IF(C23&lt;C28,"The budget will cut normal tasks short.",IF(OR((SUM(R14:R20)&gt;0),AND(C32&lt;&gt;"",C32&lt;&gt;"Unbounded",C32&gt;C23)),"The budget stops the worst case. Make sure check 3's outcome runs when it does.",IF(C32="","The worst case is not worked out yet.","The budget never binds; your caps are the only stop.")))))))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="47" ht="26" customHeight="1">
+      <c r="G45" s="14">
+        <f>(IF(C24="","Say how the budget is enforced.",IF(C24="Per call only","A per-call budget never sees the rounds add up. The task is what costs money.",IF(C24="Not enforced","Nothing stops a task at a token total.",IF(OR(C23="",C28=""),"Enter a per-task budget to check it against the two totals.",IF(C23&lt;C28,"The budget will cut normal tasks short.",IF(OR((SUM(R14:R20)&gt;0),AND(C32&lt;&gt;"",C32&lt;&gt;"Unbounded",C32&gt;C23)),"The budget stops the worst case. Make sure check 3's outcome runs when it does.",IF(C32="","The worst case is not worked out yet.","The budget never binds; your caps are the only stop."))))))))&amp;IF((IF(C24="","",IF(C24&lt;&gt;"Per task, across all rounds","Count tokens against the task, across every round, and stop the task when it crosses the budget. Then make check 3's outcome run when it does.",IF(OR(C23="",C28=""),"",IF(C23&lt;C28,"Raise the budget above the typical cost per task, or cut the round cost so a normal task fits inside it.",IF(OR((SUM(R14:R20)&gt;0),AND(C32&lt;&gt;"",C32&lt;&gt;"Unbounded",C32&gt;C23)),"",IF(C32="","","Set the budget between the typical cost and the worst case, so it actually stops a runaway task.")))))))="","",CHAR(10)&amp;"Do this: "&amp;(IF(C24="","",IF(C24&lt;&gt;"Per task, across all rounds","Count tokens against the task, across every round, and stop the task when it crosses the budget. Then make check 3's outcome run when it does.",IF(OR(C23="",C28=""),"",IF(C23&lt;C28,"Raise the budget above the typical cost per task, or cut the round cost so a normal task fits inside it.",IF(OR((SUM(R14:R20)&gt;0),AND(C32&lt;&gt;"",C32&lt;&gt;"Unbounded",C32&gt;C23)),"",IF(C32="","","Set the budget between the typical cost and the worst case, so it actually stops a runaway task."))))))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47" ht="52" customHeight="1">
       <c r="A47" s="1" t="inlineStr">
         <is>
           <t>Your next step</t>
         </is>
       </c>
-      <c r="C47" s="11">
+      <c r="C47" s="6">
         <f>IF(COUNTIF(F41:F45,"Fail")&gt;0,"Check "&amp;INDEX(A41:A45,MATCH("Fail",F41:F45,0))&amp;" — "&amp;INDEX(G41:G45,MATCH("Fail",F41:F45,0)),IF(COUNTIF(F41:F45,"Attention")&gt;0,"Check "&amp;INDEX(A41:A45,MATCH("Attention",F41:F45,0))&amp;" — "&amp;INDEX(G41:G45,MATCH("Attention",F41:F45,0)),"Nothing outstanding."))</f>
         <v/>
       </c>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="0" formatRows="1" sort="1"/>
-  <mergeCells count="52">
+  <mergeCells count="53">
     <mergeCell ref="C47:K47"/>
     <mergeCell ref="C34:D34"/>
     <mergeCell ref="B40:E40"/>
@@ -1781,6 +1786,7 @@
     <mergeCell ref="A25:B25"/>
     <mergeCell ref="D6:K6"/>
     <mergeCell ref="A37:B37"/>
+    <mergeCell ref="C39:K39"/>
     <mergeCell ref="C31:D31"/>
     <mergeCell ref="A12:K12"/>
     <mergeCell ref="D7:K7"/>
@@ -2981,6 +2987,11 @@
           <t>The five checks</t>
         </is>
       </c>
+      <c r="C39" s="13" t="inlineStr">
+        <is>
+          <t>Pass — nothing to do here.   ·   Attention — it works today, and something about it will surprise you.   ·   Fail — this is the one that stops you scaling, fix it first.</t>
+        </is>
+      </c>
     </row>
     <row r="40" ht="20" customHeight="1">
       <c r="A40" s="30" t="inlineStr">
@@ -3011,7 +3022,7 @@
       <c r="J40" s="30" t="n"/>
       <c r="K40" s="30" t="n"/>
     </row>
-    <row r="41" ht="30" customHeight="1">
+    <row r="41" ht="46" customHeight="1">
       <c r="A41" s="31" t="n">
         <v>1</v>
       </c>
@@ -3024,12 +3035,12 @@
         <f>IF(COUNTIF(B14:B20,"Yes")=0,"Not answered",IF(COUNTIFS(B14:B20,"Yes",D14:D20,"")&gt;0,"Fail","Pass"))</f>
         <v/>
       </c>
-      <c r="G41" s="13">
-        <f>IF(COUNTIF(B14:B20,"Yes")=0,"No path is marked as present yet.",IF(COUNTIFS(B14:B20,"Yes",D14:D20,"")&gt;0,"A present path has no average rounds. A path you cannot count is a path you cannot cost.","Every present path says how often it sends work back."))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="42" ht="30" customHeight="1">
+      <c r="G41" s="14">
+        <f>(IF(COUNTIF(B14:B20,"Yes")=0,"No path is marked as present yet.",IF(COUNTIFS(B14:B20,"Yes",D14:D20,"")&gt;0,"A present path has no average rounds. A path you cannot count is a path you cannot cost.","Every present path says how often it sends work back.")))&amp;IF((IF(COUNTIF(B14:B20,"Yes")=0,"",IF(COUNTIFS(B14:B20,"Yes",D14:D20,"")&gt;0,"Count send-backs divided by tasks over a normal week, from your judge verdicts, validation errors, tool errors and review queue.","")))="","",CHAR(10)&amp;"Do this: "&amp;(IF(COUNTIF(B14:B20,"Yes")=0,"",IF(COUNTIFS(B14:B20,"Yes",D14:D20,"")&gt;0,"Count send-backs divided by tasks over a normal week, from your judge verdicts, validation errors, tool errors and review queue.",""))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42" ht="46" customHeight="1">
       <c r="A42" s="31" t="n">
         <v>2</v>
       </c>
@@ -3042,12 +3053,12 @@
         <f>IF(COUNTIF(B14:B20,"Yes")=0,"Not answered",IF(COUNTIFS(B14:B20,"Yes",E14:E20,"")+COUNTIFS(B14:B20,"Yes",F14:F20,"")+COUNTIFS(B14:B20,"Yes",G14:G20,"")&gt;0,"Fail",IF(COUNTIFS(B15:B18,"Yes",G15:G18,0)&gt;0,"Attention","Pass")))</f>
         <v/>
       </c>
-      <c r="G42" s="13">
-        <f>IF(COUNTIF(B14:B20,"Yes")=0,"No path is marked as present yet.",IF(COUNTIFS(B14:B20,"Yes",E14:E20,"")+COUNTIFS(B14:B20,"Yes",F14:F20,"")+COUNTIFS(B14:B20,"Yes",G14:G20,"")&gt;0,"A present path is missing repeated, review or growth. Zero is a valid answer; blank is not.",IF(COUNTIFS(B15:B18,"Yes",G15:G18,0)&gt;0,"A judge, validation, tool or human path has no context growth. Redos usually carry more context. Check this.","Every present path has all three parts of a round.")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="43" ht="30" customHeight="1">
+      <c r="G42" s="14">
+        <f>(IF(COUNTIF(B14:B20,"Yes")=0,"No path is marked as present yet.",IF(COUNTIFS(B14:B20,"Yes",E14:E20,"")+COUNTIFS(B14:B20,"Yes",F14:F20,"")+COUNTIFS(B14:B20,"Yes",G14:G20,"")&gt;0,"A present path is missing repeated, review or growth. Zero is a valid answer; blank is not.",IF(COUNTIFS(B15:B18,"Yes",G15:G18,0)&gt;0,"A judge, validation, tool or human path has no context growth. Redos usually carry more context. Check this.","Every present path has all three parts of a round."))))&amp;IF((IF(COUNTIF(B14:B20,"Yes")=0,"",IF(COUNTIFS(B14:B20,"Yes",E14:E20,"")+COUNTIFS(B14:B20,"Yes",F14:F20,"")+COUNTIFS(B14:B20,"Yes",G14:G20,"")&gt;0,"Open one trace that was sent back and read the three figures off it: the tokens of the steps that ran again, the checker's own call, and how much bigger the redo's input was.",IF(COUNTIFS(B15:B18,"Yes",G15:G18,0)&gt;0,"Compare the input tokens of the first attempt with the redo in one trace. If the critique, the error or the rejected draft is carried forward, growth is not zero.",""))))="","",CHAR(10)&amp;"Do this: "&amp;(IF(COUNTIF(B14:B20,"Yes")=0,"",IF(COUNTIFS(B14:B20,"Yes",E14:E20,"")+COUNTIFS(B14:B20,"Yes",F14:F20,"")+COUNTIFS(B14:B20,"Yes",G14:G20,"")&gt;0,"Open one trace that was sent back and read the three figures off it: the tokens of the steps that ran again, the checker's own call, and how much bigger the redo's input was.",IF(COUNTIFS(B15:B18,"Yes",G15:G18,0)&gt;0,"Compare the input tokens of the first attempt with the redo in one trace. If the critique, the error or the rejected draft is carried forward, growth is not zero.","")))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43" ht="46" customHeight="1">
       <c r="A43" s="31" t="n">
         <v>3</v>
       </c>
@@ -3060,12 +3071,12 @@
         <f>IF(COUNTIF(B14:B20,"Yes")=0,"Not answered",IF(OR(SUM(R14:R20)&gt;0,COUNTIFS(B14:B20,"Yes",J14:J20,"")+COUNTIFS(B14:B20,"Yes",J14:J20,"Not decided")&gt;0),"Fail",IF(COUNTIFS(B14:B20,"Yes",K14:K20,"")&gt;0,"Attention","Pass")))</f>
         <v/>
       </c>
-      <c r="G43" s="13">
-        <f>IF(COUNTIF(B14:B20,"Yes")=0,"No path is marked as present yet.",IF(SUM(R14:R20)&gt;0,"A present path has no cap. Without one the worst case has no ceiling.",IF(COUNTIFS(B14:B20,"Yes",J14:J20,"")+COUNTIFS(B14:B20,"Yes",J14:J20,"Not decided")&gt;0,"A present path has no decided outcome after the last round.",IF(COUNTIFS(B14:B20,"Yes",K14:K20,"")&gt;0,"A path is capped with an outcome, but nobody owns it.","Every present path is capped, with a decided outcome and a named owner."))))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="44" ht="30" customHeight="1">
+      <c r="G43" s="14">
+        <f>(IF(COUNTIF(B14:B20,"Yes")=0,"No path is marked as present yet.",IF(SUM(R14:R20)&gt;0,"A present path has no cap. Without one the worst case has no ceiling.",IF(COUNTIFS(B14:B20,"Yes",J14:J20,"")+COUNTIFS(B14:B20,"Yes",J14:J20,"Not decided")&gt;0,"A present path has no decided outcome after the last round.",IF(COUNTIFS(B14:B20,"Yes",K14:K20,"")&gt;0,"A path is capped with an outcome, but nobody owns it.","Every present path is capped, with a decided outcome and a named owner.")))))&amp;IF((IF(COUNTIF(B14:B20,"Yes")=0,"",IF(SUM(R14:R20)&gt;0,"Set a maximum rounds per task in your orchestrator, and decide what the agent does after the last one: fail and tell the user, hand to a human, ship with a warning, or queue it.",IF(COUNTIFS(B14:B20,"Yes",J14:J20,"")+COUNTIFS(B14:B20,"Yes",J14:J20,"Not decided")&gt;0,"Decide what the agent does after the last round: fail and tell the user, hand to a human, ship with a warning, or queue it.",IF(COUNTIFS(B14:B20,"Yes",K14:K20,"")&gt;0,"Name the person or team who picks it up when that outcome fires.","")))))="","",CHAR(10)&amp;"Do this: "&amp;(IF(COUNTIF(B14:B20,"Yes")=0,"",IF(SUM(R14:R20)&gt;0,"Set a maximum rounds per task in your orchestrator, and decide what the agent does after the last one: fail and tell the user, hand to a human, ship with a warning, or queue it.",IF(COUNTIFS(B14:B20,"Yes",J14:J20,"")+COUNTIFS(B14:B20,"Yes",J14:J20,"Not decided")&gt;0,"Decide what the agent does after the last round: fail and tell the user, hand to a human, ship with a warning, or queue it.",IF(COUNTIFS(B14:B20,"Yes",K14:K20,"")&gt;0,"Name the person or team who picks it up when that outcome fires.",""))))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44" ht="46" customHeight="1">
       <c r="A44" s="31" t="n">
         <v>4</v>
       </c>
@@ -3078,12 +3089,12 @@
         <f>IF((SUM(R14:R20)&gt;0),"Fail",IF(OR(C31="",C35=""),"Not answered",IF(C31&gt;1,"Fail",IF(AND(C31&lt;=0.8,C35&lt;=1),"Pass","Attention"))))</f>
         <v/>
       </c>
-      <c r="G44" s="13">
-        <f>IF((SUM(R14:R20)&gt;0),"The worst case is unbounded, so there is no availability number to check.",IF(OR(C31="",C35=""),"Peak tasks per minute and the quota are needed for this one.",IF(C31&gt;1,"Your normal load already exceeds the quota.",IF(AND(C31&lt;=0.8,C35&lt;=1),"Normal load has headroom, and the worst case still fits.",IF(C31&lt;=0.8,"Normal load has headroom, but the worst case goes over the quota.","Normal load is above 80% of the quota. Any spike tips it over.")))))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="45" ht="30" customHeight="1">
+      <c r="G44" s="14">
+        <f>(IF((SUM(R14:R20)&gt;0),"The worst case is unbounded, so there is no availability number to check.",IF(OR(C31="",C35=""),"Peak tasks per minute and the quota are needed for this one.",IF(C31&gt;1,"Your normal load already exceeds the quota.",IF(AND(C31&lt;=0.8,C35&lt;=1),"Normal load has headroom, and the worst case still fits.",IF(C31&lt;=0.8,"Normal load has headroom, but the worst case goes over the quota.","Normal load is above 80% of the quota. Any spike tips it over."))))))&amp;IF((IF((SUM(R14:R20)&gt;0),"Cap every present path first. Until then there is no worst case to compare against the quota.",IF(OR(C31="",C35=""),"",IF(C31&gt;1,"Cut what a round costs, lower the average rounds, or raise the quota. The path with the largest average rounds times round cost is the lever; on most workflows that is the judge.",IF(AND(C31&lt;=0.8,C35&lt;=1),"",IF(C31&lt;=0.8,"Lower the caps, or add a circuit breaker that stops new work once the refusal rate crosses a threshold, so a bad minute cannot reach the worst case.","Get normal load under 80% of the quota: cut the round cost, cut the average rounds, or raise the quota."))))))="","",CHAR(10)&amp;"Do this: "&amp;(IF((SUM(R14:R20)&gt;0),"Cap every present path first. Until then there is no worst case to compare against the quota.",IF(OR(C31="",C35=""),"",IF(C31&gt;1,"Cut what a round costs, lower the average rounds, or raise the quota. The path with the largest average rounds times round cost is the lever; on most workflows that is the judge.",IF(AND(C31&lt;=0.8,C35&lt;=1),"",IF(C31&lt;=0.8,"Lower the caps, or add a circuit breaker that stops new work once the refusal rate crosses a threshold, so a bad minute cannot reach the worst case.","Get normal load under 80% of the quota: cut the round cost, cut the average rounds, or raise the quota.")))))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45" ht="46" customHeight="1">
       <c r="A45" s="31" t="n">
         <v>5</v>
       </c>
@@ -3096,25 +3107,25 @@
         <f>IF(C24="","Not answered",IF(C24&lt;&gt;"Per task, across all rounds","Fail",IF(OR(C23="",C28=""),"Not answered",IF(C23&lt;C28,"Fail",IF(OR((SUM(R14:R20)&gt;0),AND(C32&lt;&gt;"",C32&lt;&gt;"Unbounded",C32&gt;C23)),"Pass",IF(C32="","Not answered","Attention"))))))</f>
         <v/>
       </c>
-      <c r="G45" s="13">
-        <f>IF(C24="","Say how the budget is enforced.",IF(C24="Per call only","A per-call budget never sees the rounds add up. The task is what costs money.",IF(C24="Not enforced","Nothing stops a task at a token total.",IF(OR(C23="",C28=""),"Enter a per-task budget to check it against the two totals.",IF(C23&lt;C28,"The budget will cut normal tasks short.",IF(OR((SUM(R14:R20)&gt;0),AND(C32&lt;&gt;"",C32&lt;&gt;"Unbounded",C32&gt;C23)),"The budget stops the worst case. Make sure check 3's outcome runs when it does.",IF(C32="","The worst case is not worked out yet.","The budget never binds; your caps are the only stop.")))))))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="47" ht="26" customHeight="1">
+      <c r="G45" s="14">
+        <f>(IF(C24="","Say how the budget is enforced.",IF(C24="Per call only","A per-call budget never sees the rounds add up. The task is what costs money.",IF(C24="Not enforced","Nothing stops a task at a token total.",IF(OR(C23="",C28=""),"Enter a per-task budget to check it against the two totals.",IF(C23&lt;C28,"The budget will cut normal tasks short.",IF(OR((SUM(R14:R20)&gt;0),AND(C32&lt;&gt;"",C32&lt;&gt;"Unbounded",C32&gt;C23)),"The budget stops the worst case. Make sure check 3's outcome runs when it does.",IF(C32="","The worst case is not worked out yet.","The budget never binds; your caps are the only stop."))))))))&amp;IF((IF(C24="","",IF(C24&lt;&gt;"Per task, across all rounds","Count tokens against the task, across every round, and stop the task when it crosses the budget. Then make check 3's outcome run when it does.",IF(OR(C23="",C28=""),"",IF(C23&lt;C28,"Raise the budget above the typical cost per task, or cut the round cost so a normal task fits inside it.",IF(OR((SUM(R14:R20)&gt;0),AND(C32&lt;&gt;"",C32&lt;&gt;"Unbounded",C32&gt;C23)),"",IF(C32="","","Set the budget between the typical cost and the worst case, so it actually stops a runaway task.")))))))="","",CHAR(10)&amp;"Do this: "&amp;(IF(C24="","",IF(C24&lt;&gt;"Per task, across all rounds","Count tokens against the task, across every round, and stop the task when it crosses the budget. Then make check 3's outcome run when it does.",IF(OR(C23="",C28=""),"",IF(C23&lt;C28,"Raise the budget above the typical cost per task, or cut the round cost so a normal task fits inside it.",IF(OR((SUM(R14:R20)&gt;0),AND(C32&lt;&gt;"",C32&lt;&gt;"Unbounded",C32&gt;C23)),"",IF(C32="","","Set the budget between the typical cost and the worst case, so it actually stops a runaway task."))))))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47" ht="52" customHeight="1">
       <c r="A47" s="1" t="inlineStr">
         <is>
           <t>Your next step</t>
         </is>
       </c>
-      <c r="C47" s="11">
+      <c r="C47" s="6">
         <f>IF(COUNTIF(F41:F45,"Fail")&gt;0,"Check "&amp;INDEX(A41:A45,MATCH("Fail",F41:F45,0))&amp;" — "&amp;INDEX(G41:G45,MATCH("Fail",F41:F45,0)),IF(COUNTIF(F41:F45,"Attention")&gt;0,"Check "&amp;INDEX(A41:A45,MATCH("Attention",F41:F45,0))&amp;" — "&amp;INDEX(G41:G45,MATCH("Attention",F41:F45,0)),"Nothing outstanding."))</f>
         <v/>
       </c>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="0" formatRows="1" sort="1"/>
-  <mergeCells count="52">
+  <mergeCells count="53">
     <mergeCell ref="C47:K47"/>
     <mergeCell ref="C34:D34"/>
     <mergeCell ref="B40:E40"/>
@@ -3138,6 +3149,7 @@
     <mergeCell ref="A25:B25"/>
     <mergeCell ref="D6:K6"/>
     <mergeCell ref="A37:B37"/>
+    <mergeCell ref="C39:K39"/>
     <mergeCell ref="C31:D31"/>
     <mergeCell ref="A12:K12"/>
     <mergeCell ref="D7:K7"/>

--- a/public/downloads/send-back-cost-check.xlsx
+++ b/public/downloads/send-back-cost-check.xlsx
@@ -9,8 +9,9 @@
   <sheets>
     <sheet name="Start here" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Check" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="How to find these numbers" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Example" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="What each path means" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="How to find these numbers" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Example" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -145,7 +146,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -247,10 +248,16 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1496,7 +1503,7 @@
     <row r="28" ht="20" customHeight="1">
       <c r="A28" s="24" t="inlineStr">
         <is>
-          <t>Typical cost per task</t>
+          <t>Typical cost per task (tokens)</t>
         </is>
       </c>
       <c r="C28" s="25">
@@ -1505,36 +1512,46 @@
       </c>
       <c r="E28" s="13" t="inlineStr">
         <is>
-          <t>Unit economics: what every task costs on a normal day.</t>
+          <t>Unit economics: what ONE task costs on a normal day, counting the rounds sent back.</t>
         </is>
       </c>
     </row>
     <row r="29" ht="20" customHeight="1">
       <c r="A29" s="11" t="inlineStr">
         <is>
-          <t>…as a multiple of a clean run</t>
+          <t>…times what one clean run costs</t>
         </is>
       </c>
       <c r="C29" s="26">
         <f>IF(OR(C28="",C5="",C5&lt;=0),"",C28/C5)</f>
         <v/>
       </c>
+      <c r="E29" s="13" t="inlineStr">
+        <is>
+          <t>A clean run is a task nothing sent back.</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="20" customHeight="1">
       <c r="A30" s="24" t="inlineStr">
         <is>
-          <t>Typical demand at peak</t>
+          <t>Typical demand at peak (tokens per minute)</t>
         </is>
       </c>
       <c r="C30" s="27">
         <f>IF(OR(C28="",C7=""),"",C7*C28)</f>
         <v/>
       </c>
+      <c r="E30" s="13" t="inlineStr">
+        <is>
+          <t>Peak tasks per minute × the typical cost above.</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="20" customHeight="1">
       <c r="A31" s="11" t="inlineStr">
         <is>
-          <t>…as a share of the quota</t>
+          <t>…as a share of your quota</t>
         </is>
       </c>
       <c r="C31" s="28">
@@ -1545,7 +1562,7 @@
     <row r="32" ht="20" customHeight="1">
       <c r="A32" s="24" t="inlineStr">
         <is>
-          <t>Worst case per task</t>
+          <t>Worst case per task (tokens)</t>
         </is>
       </c>
       <c r="C32" s="25">
@@ -1554,14 +1571,14 @@
       </c>
       <c r="E32" s="13" t="inlineStr">
         <is>
-          <t>Availability: every loop at its cap.</t>
+          <t>Availability: ONE task with every loop run to its cap.</t>
         </is>
       </c>
     </row>
     <row r="33" ht="20" customHeight="1">
       <c r="A33" s="11" t="inlineStr">
         <is>
-          <t>…as a multiple of a clean run</t>
+          <t>…times what one clean run costs</t>
         </is>
       </c>
       <c r="C33" s="26">
@@ -1572,7 +1589,7 @@
     <row r="34" ht="20" customHeight="1">
       <c r="A34" s="24" t="inlineStr">
         <is>
-          <t>Worst case at peak</t>
+          <t>Worst case at peak (tokens per minute)</t>
         </is>
       </c>
       <c r="C34" s="27">
@@ -1583,13 +1600,18 @@
     <row r="35" ht="20" customHeight="1">
       <c r="A35" s="11" t="inlineStr">
         <is>
-          <t>…as a share of the quota</t>
+          <t>…as a share of your quota</t>
         </is>
       </c>
       <c r="C35" s="28">
         <f>IF((SUM(R14:R20)&gt;0),"Unbounded",IF(OR(C34="",C8="",C8&lt;=0),"",C34/C8))</f>
         <v/>
       </c>
+      <c r="E35" s="13" t="inlineStr">
+        <is>
+          <t>Over 100% means this workflow alone would ask for more than the pool holds.</t>
+        </is>
+      </c>
     </row>
     <row r="36" ht="20" customHeight="1">
       <c r="A36" s="24" t="inlineStr">
@@ -1603,7 +1625,7 @@
       </c>
       <c r="E36" s="13" t="inlineStr">
         <is>
-          <t>Only when a price is entered.</t>
+          <t>Only when a price is entered. Your own currency.</t>
         </is>
       </c>
     </row>
@@ -1659,16 +1681,17 @@
       <c r="J40" s="30" t="n"/>
       <c r="K40" s="30" t="n"/>
     </row>
-    <row r="41" ht="46" customHeight="1">
+    <row r="41" ht="76" customHeight="1">
       <c r="A41" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="B41" s="16" t="inlineStr">
-        <is>
-          <t>Every path that sends work back is listed</t>
-        </is>
-      </c>
-      <c r="F41" s="32">
+      <c r="B41" s="32" t="inlineStr">
+        <is>
+          <t>Every path that sends work back is listed
+A path you have not listed is spend you cannot see. Most teams count their retries and miss the judge entirely, because a judge rejection looks like normal operation rather than a failure.</t>
+        </is>
+      </c>
+      <c r="F41" s="33">
         <f>IF(COUNTIF(B14:B20,"Yes")=0,"Not answered",IF(COUNTIFS(B14:B20,"Yes",D14:D20,"")&gt;0,"Fail","Pass"))</f>
         <v/>
       </c>
@@ -1677,16 +1700,17 @@
         <v/>
       </c>
     </row>
-    <row r="42" ht="46" customHeight="1">
+    <row r="42" ht="76" customHeight="1">
       <c r="A42" s="31" t="n">
         <v>2</v>
       </c>
-      <c r="B42" s="16" t="inlineStr">
-        <is>
-          <t>Each round is costed as repeated, review and growth</t>
-        </is>
-      </c>
-      <c r="F42" s="32">
+      <c r="B42" s="32" t="inlineStr">
+        <is>
+          <t>Each round is costed as repeated, review and growth
+A round is three things and teams usually count only the first. The review call and the growing context are what make a judge loop expensive, and neither appears in a retry counter.</t>
+        </is>
+      </c>
+      <c r="F42" s="33">
         <f>IF(COUNTIF(B14:B20,"Yes")=0,"Not answered",IF(COUNTIFS(B14:B20,"Yes",E14:E20,"")+COUNTIFS(B14:B20,"Yes",F14:F20,"")+COUNTIFS(B14:B20,"Yes",G14:G20,"")&gt;0,"Fail",IF(COUNTIFS(B15:B18,"Yes",G15:G18,0)&gt;0,"Attention","Pass")))</f>
         <v/>
       </c>
@@ -1695,16 +1719,17 @@
         <v/>
       </c>
     </row>
-    <row r="43" ht="46" customHeight="1">
+    <row r="43" ht="76" customHeight="1">
       <c r="A43" s="31" t="n">
         <v>3</v>
       </c>
-      <c r="B43" s="16" t="inlineStr">
-        <is>
-          <t>Rounds are capped, and something happens after the last one</t>
-        </is>
-      </c>
-      <c r="F43" s="32">
+      <c r="B43" s="32" t="inlineStr">
+        <is>
+          <t>Rounds are capped, and something happens after the last one
+A loop with no cap has no worst case. This is the check that turns "it depends" into a number, and an uncapped path is the single most common finding here.</t>
+        </is>
+      </c>
+      <c r="F43" s="33">
         <f>IF(COUNTIF(B14:B20,"Yes")=0,"Not answered",IF(OR(SUM(R14:R20)&gt;0,COUNTIFS(B14:B20,"Yes",J14:J20,"")+COUNTIFS(B14:B20,"Yes",J14:J20,"Not decided")&gt;0),"Fail",IF(COUNTIFS(B14:B20,"Yes",K14:K20,"")&gt;0,"Attention","Pass")))</f>
         <v/>
       </c>
@@ -1713,16 +1738,17 @@
         <v/>
       </c>
     </row>
-    <row r="44" ht="46" customHeight="1">
+    <row r="44" ht="76" customHeight="1">
       <c r="A44" s="31" t="n">
         <v>4</v>
       </c>
-      <c r="B44" s="16" t="inlineStr">
-        <is>
-          <t>Two numbers: unit economics and availability</t>
-        </is>
-      </c>
-      <c r="F44" s="32">
+      <c r="B44" s="32" t="inlineStr">
+        <is>
+          <t>Two numbers: unit economics and availability
+One number is not enough, because the two failures are different. Typical cost is what you pay every day and it decides whether the product is viable. Worst case at peak decides whether a bad minute takes the system down.</t>
+        </is>
+      </c>
+      <c r="F44" s="33">
         <f>IF((SUM(R14:R20)&gt;0),"Fail",IF(OR(C31="",C35=""),"Not answered",IF(C31&gt;1,"Fail",IF(AND(C31&lt;=0.8,C35&lt;=1),"Pass","Attention"))))</f>
         <v/>
       </c>
@@ -1731,16 +1757,17 @@
         <v/>
       </c>
     </row>
-    <row r="45" ht="46" customHeight="1">
+    <row r="45" ht="76" customHeight="1">
       <c r="A45" s="31" t="n">
         <v>5</v>
       </c>
-      <c r="B45" s="16" t="inlineStr">
-        <is>
-          <t>The budget belongs to the task, across all its rounds</t>
-        </is>
-      </c>
-      <c r="F45" s="32">
+      <c r="B45" s="32" t="inlineStr">
+        <is>
+          <t>The budget belongs to the task, across all its rounds
+Tokens are spent by the task, not by the call. A per-call budget never sees three rounds add up, so it cannot stop the thing that actually runs away.</t>
+        </is>
+      </c>
+      <c r="F45" s="33">
         <f>IF(C24="","Not answered",IF(C24&lt;&gt;"Per task, across all rounds","Fail",IF(OR(C23="",C28=""),"Not answered",IF(C23&lt;C28,"Fail",IF(OR((SUM(R14:R20)&gt;0),AND(C32&lt;&gt;"",C32&lt;&gt;"Unbounded",C32&gt;C23)),"Pass",IF(C32="","Not answered","Attention"))))))</f>
         <v/>
       </c>
@@ -1762,7 +1789,7 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="0" formatRows="1" sort="1"/>
-  <mergeCells count="53">
+  <mergeCells count="56">
     <mergeCell ref="C47:K47"/>
     <mergeCell ref="C34:D34"/>
     <mergeCell ref="B40:E40"/>
@@ -1795,7 +1822,9 @@
     <mergeCell ref="A47:B47"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="A2:K2"/>
+    <mergeCell ref="E29:K29"/>
     <mergeCell ref="A32:B32"/>
+    <mergeCell ref="E35:K35"/>
     <mergeCell ref="C36:D36"/>
     <mergeCell ref="A23:B23"/>
     <mergeCell ref="G45:K45"/>
@@ -1806,6 +1835,7 @@
     <mergeCell ref="C32:D32"/>
     <mergeCell ref="A29:B29"/>
     <mergeCell ref="D8:K8"/>
+    <mergeCell ref="E30:K30"/>
     <mergeCell ref="B44:E44"/>
     <mergeCell ref="A28:B28"/>
     <mergeCell ref="C37:D37"/>
@@ -1855,6 +1885,530 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
+  <dimension ref="A1:D47"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="2.4" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="88" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="9" t="inlineStr">
+        <is>
+          <t>What each path means</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="32" customHeight="1">
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Add a path on the Check tab only if it makes the model do work a second time. That is what this workbook counts. A send-back that spends no further tokens belongs in your process notes, not here.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="B4" s="34" t="inlineStr">
+        <is>
+          <t>Transport refusal</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>The model or tool API did not answer. This is a failure to reach the service, not a problem with the output.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="16" customHeight="1">
+      <c r="C5" s="14" t="inlineStr">
+        <is>
+          <t>Examples</t>
+        </is>
+      </c>
+      <c r="D5" s="14" t="inlineStr">
+        <is>
+          <t>429 rate limit, 503 unavailable, or a timeout</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="16" customHeight="1">
+      <c r="C6" s="14" t="inlineStr">
+        <is>
+          <t>Bites</t>
+        </is>
+      </c>
+      <c r="D6" s="14" t="inlineStr">
+        <is>
+          <t>At peak only</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="16" customHeight="1">
+      <c r="C7" s="14" t="inlineStr">
+        <is>
+          <t>Context grows</t>
+        </is>
+      </c>
+      <c r="D7" s="14" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="16" customHeight="1">
+      <c r="C8" s="14" t="inlineStr">
+        <is>
+          <t>Attempt billed</t>
+        </is>
+      </c>
+      <c r="D8" s="14" t="inlineStr">
+        <is>
+          <t>Usually not for the refused call itself. The repeated steps are billed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="45" customHeight="1">
+      <c r="C9" s="35" t="inlineStr">
+        <is>
+          <t>Work repeated</t>
+        </is>
+      </c>
+      <c r="D9" s="14" t="inlineStr">
+        <is>
+          <t>Depends on what your code does next, and this is the number people get wrong. If it retries only the failed call, nothing is repeated and this is 0. If it restarts the task, it is every step that already succeeded and now runs again.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="16" customHeight="1">
+      <c r="C10" s="35" t="inlineStr">
+        <is>
+          <t>Review call</t>
+        </is>
+      </c>
+      <c r="D10" s="14" t="inlineStr">
+        <is>
+          <t>Usually 0. Nothing re-reads a call that never returned.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="16" customHeight="1">
+      <c r="C11" s="35" t="inlineStr">
+        <is>
+          <t>Context growth</t>
+        </is>
+      </c>
+      <c r="D11" s="14" t="inlineStr">
+        <is>
+          <t>Usually 0. The same request is sent again, unchanged.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="30" customHeight="1">
+      <c r="B13" s="34" t="inlineStr">
+        <is>
+          <t>Judge / critic rejection</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>A model or a rubric reads the finished output, decides it is not good enough, and sends it back with feedback.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="16" customHeight="1">
+      <c r="C14" s="14" t="inlineStr">
+        <is>
+          <t>Examples</t>
+        </is>
+      </c>
+      <c r="D14" s="14" t="inlineStr">
+        <is>
+          <t>an LLM-as-judge fails the draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="16" customHeight="1">
+      <c r="C15" s="14" t="inlineStr">
+        <is>
+          <t>Bites</t>
+        </is>
+      </c>
+      <c r="D15" s="14" t="inlineStr">
+        <is>
+          <t>Every run</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="16" customHeight="1">
+      <c r="C16" s="14" t="inlineStr">
+        <is>
+          <t>Context grows</t>
+        </is>
+      </c>
+      <c r="D16" s="14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="16" customHeight="1">
+      <c r="C17" s="14" t="inlineStr">
+        <is>
+          <t>Attempt billed</t>
+        </is>
+      </c>
+      <c r="D17" s="14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="16" customHeight="1">
+      <c r="C18" s="35" t="inlineStr">
+        <is>
+          <t>Work repeated</t>
+        </is>
+      </c>
+      <c r="D18" s="14" t="inlineStr">
+        <is>
+          <t>The steps that produce the output again. Often just the drafting step rather than the whole task.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="30" customHeight="1">
+      <c r="C19" s="35" t="inlineStr">
+        <is>
+          <t>Review call</t>
+        </is>
+      </c>
+      <c r="D19" s="14" t="inlineStr">
+        <is>
+          <t>The judge's own call, on the new attempt. It reads the whole output plus its rubric, so its input is usually large. This is the line teams forget.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="16" customHeight="1">
+      <c r="C20" s="35" t="inlineStr">
+        <is>
+          <t>Context growth</t>
+        </is>
+      </c>
+      <c r="D20" s="14" t="inlineStr">
+        <is>
+          <t>The critique carried into the redo, so the next attempt has more input than the one it replaced.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="30" customHeight="1">
+      <c r="B22" s="34" t="inlineStr">
+        <is>
+          <t>Validation failure</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>The output did not parse, did not match the schema, or tripped a guardrail, so the model has to produce it again.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="16" customHeight="1">
+      <c r="C23" s="14" t="inlineStr">
+        <is>
+          <t>Examples</t>
+        </is>
+      </c>
+      <c r="D23" s="14" t="inlineStr">
+        <is>
+          <t>bad JSON, schema mismatch, guardrail trip</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="16" customHeight="1">
+      <c r="C24" s="14" t="inlineStr">
+        <is>
+          <t>Bites</t>
+        </is>
+      </c>
+      <c r="D24" s="14" t="inlineStr">
+        <is>
+          <t>Every run</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="16" customHeight="1">
+      <c r="C25" s="14" t="inlineStr">
+        <is>
+          <t>Context grows</t>
+        </is>
+      </c>
+      <c r="D25" s="14" t="inlineStr">
+        <is>
+          <t>Usually</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="16" customHeight="1">
+      <c r="C26" s="14" t="inlineStr">
+        <is>
+          <t>Attempt billed</t>
+        </is>
+      </c>
+      <c r="D26" s="14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="16" customHeight="1">
+      <c r="C27" s="35" t="inlineStr">
+        <is>
+          <t>Work repeated</t>
+        </is>
+      </c>
+      <c r="D27" s="14" t="inlineStr">
+        <is>
+          <t>The step that produced the invalid output.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="30" customHeight="1">
+      <c r="C28" s="35" t="inlineStr">
+        <is>
+          <t>Review call</t>
+        </is>
+      </c>
+      <c r="D28" s="14" t="inlineStr">
+        <is>
+          <t>The validator's own cost. It is 0 when the check is code, such as a JSON schema check, rather than a model.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="16" customHeight="1">
+      <c r="C29" s="35" t="inlineStr">
+        <is>
+          <t>Context growth</t>
+        </is>
+      </c>
+      <c r="D29" s="14" t="inlineStr">
+        <is>
+          <t>The error message handed back so the model knows what to fix.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="30" customHeight="1">
+      <c r="B31" s="34" t="inlineStr">
+        <is>
+          <t>Tool error</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="inlineStr">
+        <is>
+          <t>A tool the agent called returned an error: not found, permission denied, bad arguments. The agent has to re-plan or try again.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="16" customHeight="1">
+      <c r="C32" s="14" t="inlineStr">
+        <is>
+          <t>Examples</t>
+        </is>
+      </c>
+      <c r="D32" s="14" t="inlineStr">
+        <is>
+          <t>not found, permission denied, bad arguments</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="16" customHeight="1">
+      <c r="C33" s="14" t="inlineStr">
+        <is>
+          <t>Bites</t>
+        </is>
+      </c>
+      <c r="D33" s="14" t="inlineStr">
+        <is>
+          <t>Every run</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="16" customHeight="1">
+      <c r="C34" s="14" t="inlineStr">
+        <is>
+          <t>Context grows</t>
+        </is>
+      </c>
+      <c r="D34" s="14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="16" customHeight="1">
+      <c r="C35" s="14" t="inlineStr">
+        <is>
+          <t>Attempt billed</t>
+        </is>
+      </c>
+      <c r="D35" s="14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="16" customHeight="1">
+      <c r="C36" s="35" t="inlineStr">
+        <is>
+          <t>Work repeated</t>
+        </is>
+      </c>
+      <c r="D36" s="14" t="inlineStr">
+        <is>
+          <t>The reasoning steps that run again to work out what to do instead.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="16" customHeight="1">
+      <c r="C37" s="35" t="inlineStr">
+        <is>
+          <t>Review call</t>
+        </is>
+      </c>
+      <c r="D37" s="14" t="inlineStr">
+        <is>
+          <t>Usually 0, unless something checks the new plan before it runs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="16" customHeight="1">
+      <c r="C38" s="35" t="inlineStr">
+        <is>
+          <t>Context growth</t>
+        </is>
+      </c>
+      <c r="D38" s="14" t="inlineStr">
+        <is>
+          <t>The error text and the failed attempt, carried into the next plan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="18" customHeight="1">
+      <c r="B40" s="34" t="inlineStr">
+        <is>
+          <t>Human rejection</t>
+        </is>
+      </c>
+      <c r="C40" s="6" t="inlineStr">
+        <is>
+          <t>A person reviewing the work sends it back. Their reading costs no tokens; the redo does.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="16" customHeight="1">
+      <c r="C41" s="14" t="inlineStr">
+        <is>
+          <t>Examples</t>
+        </is>
+      </c>
+      <c r="D41" s="14" t="inlineStr">
+        <is>
+          <t>a maker-checker sends it back</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="16" customHeight="1">
+      <c r="C42" s="14" t="inlineStr">
+        <is>
+          <t>Bites</t>
+        </is>
+      </c>
+      <c r="D42" s="14" t="inlineStr">
+        <is>
+          <t>Every run</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="16" customHeight="1">
+      <c r="C43" s="14" t="inlineStr">
+        <is>
+          <t>Context grows</t>
+        </is>
+      </c>
+      <c r="D43" s="14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="16" customHeight="1">
+      <c r="C44" s="14" t="inlineStr">
+        <is>
+          <t>Attempt billed</t>
+        </is>
+      </c>
+      <c r="D44" s="14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="16" customHeight="1">
+      <c r="C45" s="35" t="inlineStr">
+        <is>
+          <t>Work repeated</t>
+        </is>
+      </c>
+      <c r="D45" s="14" t="inlineStr">
+        <is>
+          <t>The steps that run again to produce a new version.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="16" customHeight="1">
+      <c r="C46" s="35" t="inlineStr">
+        <is>
+          <t>Review call</t>
+        </is>
+      </c>
+      <c r="D46" s="14" t="inlineStr">
+        <is>
+          <t>0. A person reading the output consumes no tokens.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="16" customHeight="1">
+      <c r="C47" s="35" t="inlineStr">
+        <is>
+          <t>Context growth</t>
+        </is>
+      </c>
+      <c r="D47" s="14" t="inlineStr">
+        <is>
+          <t>The reviewer's comments, carried into the redo.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="0" formatRows="1" sort="1"/>
+  <mergeCells count="6">
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="C40:D40"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="C4:D4"/>
+  </mergeCells>
+  <pageMargins left="0.4" right="0.4" top="0.4" bottom="0.4" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:C46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -1878,7 +2432,7 @@
       </c>
     </row>
     <row r="4" ht="28" customHeight="1">
-      <c r="B4" s="33" t="inlineStr">
+      <c r="B4" s="34" t="inlineStr">
         <is>
           <t>Tokens for one clean run</t>
         </is>
@@ -1904,7 +2458,7 @@
       </c>
     </row>
     <row r="8" ht="28" customHeight="1">
-      <c r="B8" s="33" t="inlineStr">
+      <c r="B8" s="34" t="inlineStr">
         <is>
           <t>Always-on checks</t>
         </is>
@@ -1923,7 +2477,7 @@
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
-      <c r="B11" s="33" t="inlineStr">
+      <c r="B11" s="34" t="inlineStr">
         <is>
           <t>Average rounds per task, per path</t>
         </is>
@@ -1970,7 +2524,7 @@
       </c>
     </row>
     <row r="18" ht="28" customHeight="1">
-      <c r="B18" s="33" t="inlineStr">
+      <c r="B18" s="34" t="inlineStr">
         <is>
           <t>Work repeated</t>
         </is>
@@ -2003,7 +2557,7 @@
       </c>
     </row>
     <row r="23" ht="16" customHeight="1">
-      <c r="B23" s="33" t="inlineStr">
+      <c r="B23" s="34" t="inlineStr">
         <is>
           <t>Review call</t>
         </is>
@@ -2022,7 +2576,7 @@
       </c>
     </row>
     <row r="26" ht="42" customHeight="1">
-      <c r="B26" s="33" t="inlineStr">
+      <c r="B26" s="34" t="inlineStr">
         <is>
           <t>Context growth</t>
         </is>
@@ -2041,7 +2595,7 @@
       </c>
     </row>
     <row r="29" ht="28" customHeight="1">
-      <c r="B29" s="33" t="inlineStr">
+      <c r="B29" s="34" t="inlineStr">
         <is>
           <t>Max rounds per task</t>
         </is>
@@ -2060,7 +2614,7 @@
       </c>
     </row>
     <row r="32" ht="28" customHeight="1">
-      <c r="B32" s="33" t="inlineStr">
+      <c r="B32" s="34" t="inlineStr">
         <is>
           <t>Peak tasks per minute</t>
         </is>
@@ -2079,7 +2633,7 @@
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
-      <c r="B35" s="33" t="inlineStr">
+      <c r="B35" s="34" t="inlineStr">
         <is>
           <t>Tokens-per-minute quota</t>
         </is>
@@ -2105,7 +2659,7 @@
       </c>
     </row>
     <row r="39" ht="16" customHeight="1">
-      <c r="B39" s="33" t="inlineStr">
+      <c r="B39" s="34" t="inlineStr">
         <is>
           <t>Per-task budget</t>
         </is>
@@ -2124,7 +2678,7 @@
       </c>
     </row>
     <row r="42" ht="16" customHeight="1">
-      <c r="B42" s="33" t="inlineStr">
+      <c r="B42" s="34" t="inlineStr">
         <is>
           <t>Price per million tokens</t>
         </is>
@@ -2143,7 +2697,7 @@
       </c>
     </row>
     <row r="45" ht="16" customHeight="1">
-      <c r="B45" s="33" t="inlineStr">
+      <c r="B45" s="34" t="inlineStr">
         <is>
           <t>No data yet?</t>
         </is>
@@ -2203,7 +2757,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2859,7 +3413,7 @@
     <row r="28" ht="20" customHeight="1">
       <c r="A28" s="24" t="inlineStr">
         <is>
-          <t>Typical cost per task</t>
+          <t>Typical cost per task (tokens)</t>
         </is>
       </c>
       <c r="C28" s="25">
@@ -2868,36 +3422,46 @@
       </c>
       <c r="E28" s="13" t="inlineStr">
         <is>
-          <t>Unit economics: what every task costs on a normal day.</t>
+          <t>Unit economics: what ONE task costs on a normal day, counting the rounds sent back.</t>
         </is>
       </c>
     </row>
     <row r="29" ht="20" customHeight="1">
       <c r="A29" s="11" t="inlineStr">
         <is>
-          <t>…as a multiple of a clean run</t>
+          <t>…times what one clean run costs</t>
         </is>
       </c>
       <c r="C29" s="26">
         <f>IF(OR(C28="",C5="",C5&lt;=0),"",C28/C5)</f>
         <v/>
       </c>
+      <c r="E29" s="13" t="inlineStr">
+        <is>
+          <t>A clean run is a task nothing sent back.</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="20" customHeight="1">
       <c r="A30" s="24" t="inlineStr">
         <is>
-          <t>Typical demand at peak</t>
+          <t>Typical demand at peak (tokens per minute)</t>
         </is>
       </c>
       <c r="C30" s="27">
         <f>IF(OR(C28="",C7=""),"",C7*C28)</f>
         <v/>
       </c>
+      <c r="E30" s="13" t="inlineStr">
+        <is>
+          <t>Peak tasks per minute × the typical cost above.</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="20" customHeight="1">
       <c r="A31" s="11" t="inlineStr">
         <is>
-          <t>…as a share of the quota</t>
+          <t>…as a share of your quota</t>
         </is>
       </c>
       <c r="C31" s="28">
@@ -2908,7 +3472,7 @@
     <row r="32" ht="20" customHeight="1">
       <c r="A32" s="24" t="inlineStr">
         <is>
-          <t>Worst case per task</t>
+          <t>Worst case per task (tokens)</t>
         </is>
       </c>
       <c r="C32" s="25">
@@ -2917,14 +3481,14 @@
       </c>
       <c r="E32" s="13" t="inlineStr">
         <is>
-          <t>Availability: every loop at its cap.</t>
+          <t>Availability: ONE task with every loop run to its cap.</t>
         </is>
       </c>
     </row>
     <row r="33" ht="20" customHeight="1">
       <c r="A33" s="11" t="inlineStr">
         <is>
-          <t>…as a multiple of a clean run</t>
+          <t>…times what one clean run costs</t>
         </is>
       </c>
       <c r="C33" s="26">
@@ -2935,7 +3499,7 @@
     <row r="34" ht="20" customHeight="1">
       <c r="A34" s="24" t="inlineStr">
         <is>
-          <t>Worst case at peak</t>
+          <t>Worst case at peak (tokens per minute)</t>
         </is>
       </c>
       <c r="C34" s="27">
@@ -2946,13 +3510,18 @@
     <row r="35" ht="20" customHeight="1">
       <c r="A35" s="11" t="inlineStr">
         <is>
-          <t>…as a share of the quota</t>
+          <t>…as a share of your quota</t>
         </is>
       </c>
       <c r="C35" s="28">
         <f>IF((SUM(R14:R20)&gt;0),"Unbounded",IF(OR(C34="",C8="",C8&lt;=0),"",C34/C8))</f>
         <v/>
       </c>
+      <c r="E35" s="13" t="inlineStr">
+        <is>
+          <t>Over 100% means this workflow alone would ask for more than the pool holds.</t>
+        </is>
+      </c>
     </row>
     <row r="36" ht="20" customHeight="1">
       <c r="A36" s="24" t="inlineStr">
@@ -2966,7 +3535,7 @@
       </c>
       <c r="E36" s="13" t="inlineStr">
         <is>
-          <t>Only when a price is entered.</t>
+          <t>Only when a price is entered. Your own currency.</t>
         </is>
       </c>
     </row>
@@ -3022,16 +3591,17 @@
       <c r="J40" s="30" t="n"/>
       <c r="K40" s="30" t="n"/>
     </row>
-    <row r="41" ht="46" customHeight="1">
+    <row r="41" ht="76" customHeight="1">
       <c r="A41" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="B41" s="16" t="inlineStr">
-        <is>
-          <t>Every path that sends work back is listed</t>
-        </is>
-      </c>
-      <c r="F41" s="32">
+      <c r="B41" s="32" t="inlineStr">
+        <is>
+          <t>Every path that sends work back is listed
+A path you have not listed is spend you cannot see. Most teams count their retries and miss the judge entirely, because a judge rejection looks like normal operation rather than a failure.</t>
+        </is>
+      </c>
+      <c r="F41" s="33">
         <f>IF(COUNTIF(B14:B20,"Yes")=0,"Not answered",IF(COUNTIFS(B14:B20,"Yes",D14:D20,"")&gt;0,"Fail","Pass"))</f>
         <v/>
       </c>
@@ -3040,16 +3610,17 @@
         <v/>
       </c>
     </row>
-    <row r="42" ht="46" customHeight="1">
+    <row r="42" ht="76" customHeight="1">
       <c r="A42" s="31" t="n">
         <v>2</v>
       </c>
-      <c r="B42" s="16" t="inlineStr">
-        <is>
-          <t>Each round is costed as repeated, review and growth</t>
-        </is>
-      </c>
-      <c r="F42" s="32">
+      <c r="B42" s="32" t="inlineStr">
+        <is>
+          <t>Each round is costed as repeated, review and growth
+A round is three things and teams usually count only the first. The review call and the growing context are what make a judge loop expensive, and neither appears in a retry counter.</t>
+        </is>
+      </c>
+      <c r="F42" s="33">
         <f>IF(COUNTIF(B14:B20,"Yes")=0,"Not answered",IF(COUNTIFS(B14:B20,"Yes",E14:E20,"")+COUNTIFS(B14:B20,"Yes",F14:F20,"")+COUNTIFS(B14:B20,"Yes",G14:G20,"")&gt;0,"Fail",IF(COUNTIFS(B15:B18,"Yes",G15:G18,0)&gt;0,"Attention","Pass")))</f>
         <v/>
       </c>
@@ -3058,16 +3629,17 @@
         <v/>
       </c>
     </row>
-    <row r="43" ht="46" customHeight="1">
+    <row r="43" ht="76" customHeight="1">
       <c r="A43" s="31" t="n">
         <v>3</v>
       </c>
-      <c r="B43" s="16" t="inlineStr">
-        <is>
-          <t>Rounds are capped, and something happens after the last one</t>
-        </is>
-      </c>
-      <c r="F43" s="32">
+      <c r="B43" s="32" t="inlineStr">
+        <is>
+          <t>Rounds are capped, and something happens after the last one
+A loop with no cap has no worst case. This is the check that turns "it depends" into a number, and an uncapped path is the single most common finding here.</t>
+        </is>
+      </c>
+      <c r="F43" s="33">
         <f>IF(COUNTIF(B14:B20,"Yes")=0,"Not answered",IF(OR(SUM(R14:R20)&gt;0,COUNTIFS(B14:B20,"Yes",J14:J20,"")+COUNTIFS(B14:B20,"Yes",J14:J20,"Not decided")&gt;0),"Fail",IF(COUNTIFS(B14:B20,"Yes",K14:K20,"")&gt;0,"Attention","Pass")))</f>
         <v/>
       </c>
@@ -3076,16 +3648,17 @@
         <v/>
       </c>
     </row>
-    <row r="44" ht="46" customHeight="1">
+    <row r="44" ht="76" customHeight="1">
       <c r="A44" s="31" t="n">
         <v>4</v>
       </c>
-      <c r="B44" s="16" t="inlineStr">
-        <is>
-          <t>Two numbers: unit economics and availability</t>
-        </is>
-      </c>
-      <c r="F44" s="32">
+      <c r="B44" s="32" t="inlineStr">
+        <is>
+          <t>Two numbers: unit economics and availability
+One number is not enough, because the two failures are different. Typical cost is what you pay every day and it decides whether the product is viable. Worst case at peak decides whether a bad minute takes the system down.</t>
+        </is>
+      </c>
+      <c r="F44" s="33">
         <f>IF((SUM(R14:R20)&gt;0),"Fail",IF(OR(C31="",C35=""),"Not answered",IF(C31&gt;1,"Fail",IF(AND(C31&lt;=0.8,C35&lt;=1),"Pass","Attention"))))</f>
         <v/>
       </c>
@@ -3094,16 +3667,17 @@
         <v/>
       </c>
     </row>
-    <row r="45" ht="46" customHeight="1">
+    <row r="45" ht="76" customHeight="1">
       <c r="A45" s="31" t="n">
         <v>5</v>
       </c>
-      <c r="B45" s="16" t="inlineStr">
-        <is>
-          <t>The budget belongs to the task, across all its rounds</t>
-        </is>
-      </c>
-      <c r="F45" s="32">
+      <c r="B45" s="32" t="inlineStr">
+        <is>
+          <t>The budget belongs to the task, across all its rounds
+Tokens are spent by the task, not by the call. A per-call budget never sees three rounds add up, so it cannot stop the thing that actually runs away.</t>
+        </is>
+      </c>
+      <c r="F45" s="33">
         <f>IF(C24="","Not answered",IF(C24&lt;&gt;"Per task, across all rounds","Fail",IF(OR(C23="",C28=""),"Not answered",IF(C23&lt;C28,"Fail",IF(OR((SUM(R14:R20)&gt;0),AND(C32&lt;&gt;"",C32&lt;&gt;"Unbounded",C32&gt;C23)),"Pass",IF(C32="","Not answered","Attention"))))))</f>
         <v/>
       </c>
@@ -3125,7 +3699,7 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="0" formatRows="1" sort="1"/>
-  <mergeCells count="53">
+  <mergeCells count="56">
     <mergeCell ref="C47:K47"/>
     <mergeCell ref="C34:D34"/>
     <mergeCell ref="B40:E40"/>
@@ -3158,7 +3732,9 @@
     <mergeCell ref="A47:B47"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="A2:K2"/>
+    <mergeCell ref="E29:K29"/>
     <mergeCell ref="A32:B32"/>
+    <mergeCell ref="E35:K35"/>
     <mergeCell ref="C36:D36"/>
     <mergeCell ref="A23:B23"/>
     <mergeCell ref="G45:K45"/>
@@ -3169,6 +3745,7 @@
     <mergeCell ref="C32:D32"/>
     <mergeCell ref="A29:B29"/>
     <mergeCell ref="D8:K8"/>
+    <mergeCell ref="E30:K30"/>
     <mergeCell ref="B44:E44"/>
     <mergeCell ref="A28:B28"/>
     <mergeCell ref="C37:D37"/>

--- a/public/downloads/send-back-cost-check.xlsx
+++ b/public/downloads/send-back-cost-check.xlsx
@@ -1480,7 +1480,7 @@
       </c>
       <c r="C24" s="8" t="n"/>
     </row>
-    <row r="25">
+    <row r="25" ht="32" customHeight="1">
       <c r="A25" s="11" t="inlineStr">
         <is>
           <t>Blended price per million tokens (optional)</t>
@@ -1489,7 +1489,7 @@
       <c r="C25" s="23" t="n"/>
       <c r="E25" s="13" t="inlineStr">
         <is>
-          <t>Your own currency. The workbook shows no symbol.</t>
+          <t>Optional, and blank in the Example on purpose: a blended rate depends on your provider, your tier and your own mix of input and output tokens, so nobody else can supply it. Enter yours and the two cost rows below fill in. Your own currency; no symbol is shown.</t>
         </is>
       </c>
     </row>
@@ -1625,7 +1625,7 @@
       </c>
       <c r="E36" s="13" t="inlineStr">
         <is>
-          <t>Only when a price is entered. Your own currency.</t>
+          <t>Blank until a price is entered above. Everything else on this sheet is in tokens.</t>
         </is>
       </c>
     </row>
@@ -1725,7 +1725,7 @@
       </c>
       <c r="B43" s="32" t="inlineStr">
         <is>
-          <t>Rounds are capped, and something happens after the last one
+          <t>Every loop has a limit, a decided outcome, and an owner
 A loop with no cap has no worst case. This is the check that turns "it depends" into a number, and an uncapped path is the single most common finding here.</t>
         </is>
       </c>
@@ -1744,8 +1744,8 @@
       </c>
       <c r="B44" s="32" t="inlineStr">
         <is>
-          <t>Two numbers: unit economics and availability
-One number is not enough, because the two failures are different. Typical cost is what you pay every day and it decides whether the product is viable. Worst case at peak decides whether a bad minute takes the system down.</t>
+          <t>Both numbers fit: what you pay daily, and your busiest minute
+One number is not enough, because the two ways this hurts you are different. The typical cost is what you pay every day, and it decides whether the product makes money. The worst case at peak decides whether one bad minute takes the whole system down. A workflow can be fine on one and fatal on the other.</t>
         </is>
       </c>
       <c r="F44" s="33">
@@ -1763,8 +1763,8 @@
       </c>
       <c r="B45" s="32" t="inlineStr">
         <is>
-          <t>The budget belongs to the task, across all its rounds
-Tokens are spent by the task, not by the call. A per-call budget never sees three rounds add up, so it cannot stop the thing that actually runs away.</t>
+          <t>One token budget for the whole task, not one per call
+A task that goes round three times spends three times. A budget checked on each call sees the attempts one at a time and never sees the total, so it cannot stop a task that is running away. To do that, every round has to count against one limit that belongs to the task.</t>
         </is>
       </c>
       <c r="F45" s="33">
@@ -3390,7 +3390,7 @@
         </is>
       </c>
     </row>
-    <row r="25">
+    <row r="25" ht="32" customHeight="1">
       <c r="A25" s="11" t="inlineStr">
         <is>
           <t>Blended price per million tokens (optional)</t>
@@ -3399,7 +3399,7 @@
       <c r="C25" s="23" t="n"/>
       <c r="E25" s="13" t="inlineStr">
         <is>
-          <t>Your own currency. The workbook shows no symbol.</t>
+          <t>Optional, and blank in the Example on purpose: a blended rate depends on your provider, your tier and your own mix of input and output tokens, so nobody else can supply it. Enter yours and the two cost rows below fill in. Your own currency; no symbol is shown.</t>
         </is>
       </c>
     </row>
@@ -3535,7 +3535,7 @@
       </c>
       <c r="E36" s="13" t="inlineStr">
         <is>
-          <t>Only when a price is entered. Your own currency.</t>
+          <t>Blank until a price is entered above. Everything else on this sheet is in tokens.</t>
         </is>
       </c>
     </row>
@@ -3635,7 +3635,7 @@
       </c>
       <c r="B43" s="32" t="inlineStr">
         <is>
-          <t>Rounds are capped, and something happens after the last one
+          <t>Every loop has a limit, a decided outcome, and an owner
 A loop with no cap has no worst case. This is the check that turns "it depends" into a number, and an uncapped path is the single most common finding here.</t>
         </is>
       </c>
@@ -3654,8 +3654,8 @@
       </c>
       <c r="B44" s="32" t="inlineStr">
         <is>
-          <t>Two numbers: unit economics and availability
-One number is not enough, because the two failures are different. Typical cost is what you pay every day and it decides whether the product is viable. Worst case at peak decides whether a bad minute takes the system down.</t>
+          <t>Both numbers fit: what you pay daily, and your busiest minute
+One number is not enough, because the two ways this hurts you are different. The typical cost is what you pay every day, and it decides whether the product makes money. The worst case at peak decides whether one bad minute takes the whole system down. A workflow can be fine on one and fatal on the other.</t>
         </is>
       </c>
       <c r="F44" s="33">
@@ -3673,8 +3673,8 @@
       </c>
       <c r="B45" s="32" t="inlineStr">
         <is>
-          <t>The budget belongs to the task, across all its rounds
-Tokens are spent by the task, not by the call. A per-call budget never sees three rounds add up, so it cannot stop the thing that actually runs away.</t>
+          <t>One token budget for the whole task, not one per call
+A task that goes round three times spends three times. A budget checked on each call sees the attempts one at a time and never sees the total, so it cannot stop a task that is running away. To do that, every round has to count against one limit that belongs to the task.</t>
         </is>
       </c>
       <c r="F45" s="33">
